--- a/04_DESIGN_TABLES/DesignTable_2503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2503.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A2: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A2: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=0.69~0.690; N2@DRIVE=0.52~0.520; Y@REF=0.44~0.438; D@BORE=0.06~0.062; D1@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A3: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending; page prints B "3/8-14" and A "1/8-24" (thread typos: 3/8-24 UNF / 1/8-27 NPTF intended) - as-printed in Threads note, corrected values used per MS51508 A3</t>
+          <t>legs diverge from MS51508 A3: AW M2=0.69/N2=0.52 vs MS 0.66/0.52 - AW stands (dimension authority), Brennan tiebreak pending; page prints B "3/8-14" and A "1/8-24" (thread typos: 3/8-24 UNF / 1/8-27 NPTF intended) - as-printed in Threads note, corrected values used per MS51508 A3 | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=0.69~0.690; N2@DRIVE=0.52~0.520; Y@REF=0.44~0.438; D@BORE=0.13~0.125; D1@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1325,7 +1325,7 @@
         <v>0.82</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J)</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.95</v>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J)</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>1.17</v>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J)</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending</t>
+          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3126,7 +3126,11 @@
           <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J)</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.42~1.420; N2@DRIVE=1.48~1.480; Y@REF=1.31~1.312; D@BORE=0.61~0.609; D1@BORE=0.94~0.938</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -3410,7 +3414,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>B printed "1 1/16-12" (a -16 tube takes 1 5/16-12; non-FG row prints it) - as-printed in Threads note</t>
+          <t>B printed "1 1/16-12" (a -16 tube takes 1 5/16-12; non-FG row prints it) - as-printed in Threads note | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.54~1.540; N2@DRIVE=1.67~1.670; Y@REF=1.63~1.625; D@BORE=0.84~0.844; D1@BORE=1.25~1.250</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3590,7 +3594,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -3600,7 +3604,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>TUBE OD printed "1" (a -20 is 1 1/4; non-FG row prints it) - as-printed</t>
+          <t>TUBE OD printed "1" (a -20 is 1 1/4; non-FG row prints it) - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M2@DRIVE=1.59~1.590; N2@DRIVE=1.64~1.640; Y@REF=1.63~1.625; D@BORE=1.08~1.078; D1@BORE=0.94~0.938</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1158,7 +1158,7 @@
         <v>0.17</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.531</v>
+        <v>0.52</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0.4375</v>
@@ -1183,10 +1183,14 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X755 Side 2 ID = 0.531 (table had 0.52) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr"/>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X755 Side 2 ID = 0.531 (table had 0.52) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.52 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.531) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.531 -&gt; Air-Way 0.52</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1325,7 +1329,7 @@
         <v>0.82</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -1359,12 +1363,12 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19]</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P757 = 0.860 (table had 0.88) [user 2026-10-18 A19]; N2@DRIVE: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.86) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086)</t>
+          <t>legs diverge from MS51508 A5-4: AW M2=0.82/N2=0.88 vs MS 0.82/0.86 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.88 -&gt; OMi 0.860 (Items!P757, M086) | 2026-10-20 Air-Way first: N2@DRIVE OMi/Brennan 0.86 -&gt; Air-Way 0.88</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1734,7 +1738,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.95</v>
@@ -1771,12 +1775,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19]</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N759 = 0.870 (table had 0.91) [user 2026-10-18 A19]; M2@DRIVE: Air-Way 0.91 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.87) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085)</t>
+          <t>legs diverge from MS51508 A6-6: AW M2=0.91/N2=0.95 vs MS 0.87/0.95 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 0.91 -&gt; OMi 0.870 (Items!N759, M085) | 2026-10-20 Air-Way first: M2@DRIVE OMi/Brennan 0.87 -&gt; Air-Way 0.91</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2264,7 +2268,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>1.17</v>
@@ -2301,12 +2305,12 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19]</t>
+          <t>MS51508E Amd1 corroborates FG rows (24-row map); JIC end axials VERIFIED lib-wide (MS33656J); M2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N763 = 0.990 (table had 1.11) [user 2026-10-18 A19]; M2@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085)</t>
+          <t>legs diverge from MS51508 A8-8: AW M2=1.11/N2=1.17 vs MS 0.99/1.17 - AW stands (dimension authority), Brennan tiebreak pending | A19 (user 2026-10-18, group 2 settled): M2@DRIVE 1.11 -&gt; OMi 0.990 (Items!N763, M085) | 2026-10-20 Air-Way first: M2@DRIVE OMi/Brennan 0.99 -&gt; Air-Way 1.11</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
